--- a/Test cases of Globewest/Sprint 3 - Homepage Test Cases.xlsx
+++ b/Test cases of Globewest/Sprint 3 - Homepage Test Cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="QA Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,18 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K22"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="64.83203125" customWidth="1"/>
-    <col min="5" max="5" width="64.83203125" customWidth="1"/>
-    <col min="6" max="6" width="64.83203125" customWidth="1"/>
-    <col min="7" max="7" width="64.83203125" customWidth="1"/>
-    <col min="8" max="8" width="64.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="64.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="45.83203125" customWidth="1"/>
+    <col min="7" max="7" width="45.83203125" customWidth="1"/>
+    <col min="8" max="8" width="45.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,6 +443,9 @@
       <c r="J1" t="str">
         <v>Defect Summary</v>
       </c>
+      <c r="K1" t="str">
+        <v>Visual Evidence</v>
+      </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
@@ -460,9 +464,9 @@
         <v>US Staging storefront accessible (https://mcstaging2.globewest.com/)</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to US Homepage
-2. Inspect document.title and HTML head meta tags
-3. Verify presence of "GlobeWest USA" brand keywords</v>
+        <v xml:space="preserve">Step 1: Navigate to US Homepage
+Step 2: Inspect document.title and HTML head meta tags
+Step 3: Verify presence of "GlobeWest USA" brand keywords</v>
       </c>
       <c r="G2" t="str">
         <v>Document title displays branded title, e.g. "GlobeWest USA | Distinctive Living Furniture &amp; Homewares"</v>
@@ -475,6 +479,9 @@
       </c>
       <c r="J2" t="str">
         <v>None. Verified acceptable for staging environment.</v>
+      </c>
+      <c r="K2" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -494,9 +501,9 @@
         <v>User is in anonymous/guest browsing mode</v>
       </c>
       <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load US Homepage
-2. Inspect top utility bar links
-3. Verify "Become a Trade Customer" and "Book Showroom" CTAs</v>
+        <v xml:space="preserve">Step 1: Load US Homepage
+Step 2: Inspect top utility bar links
+Step 3: Verify "Become a Trade Customer" and "Book Showroom" CTAs</v>
       </c>
       <c r="G3" t="str">
         <v>Utility bar renders "Become a Trade Customer" link and "Book Showroom Appointment". Wholesale prices masked.</v>
@@ -509,6 +516,9 @@
       </c>
       <c r="J3" t="str">
         <v>None. Verified matching approved specification.</v>
+      </c>
+      <c r="K3" t="str">
+        <v>screenshots/desktop/02_desktop_utility_bar.png</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -528,9 +538,9 @@
         <v>US Staging storefront loaded at 1440x900</v>
       </c>
       <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to top hero slider
-2. Verify Swiper container, active slide imagery, and typography
-3. Check pagination bullets and slide change transitions</v>
+        <v xml:space="preserve">Step 1: Scroll to top hero slider
+Step 2: Verify Swiper container, active slide imagery, and typography
+Step 3: Check pagination bullets and slide change transitions</v>
       </c>
       <c r="G4" t="str">
         <v>Hero slider renders high-resolution lifestyle photography, title, subtitle, and primary call-to-action button.</v>
@@ -543,6 +553,9 @@
       </c>
       <c r="J4" t="str">
         <v>None. Verified matching AU design baseline.</v>
+      </c>
+      <c r="K4" t="str">
+        <v>comparison/COMPARISON_PASS_01_HERO_BANNER_SLIDER.png</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -562,9 +575,9 @@
         <v>Hero slider is visible</v>
       </c>
       <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect primary button "Explore Collections 2025 Volume #02"
-2. Verify target href attribute
-3. Click button and observe target destination URL</v>
+        <v xml:space="preserve">Step 1: Inspect primary button "Explore Collections 2025 Volume #02"
+Step 2: Verify target href attribute
+Step 3: Click button and observe target destination URL</v>
       </c>
       <c r="G5" t="str">
         <v>CTA button navigates internally to US catalog destination without redirection to Australian domain.</v>
@@ -577,6 +590,9 @@
       </c>
       <c r="J5" t="str">
         <v>None. Previous Ticket 4 defect successfully resolved.</v>
+      </c>
+      <c r="K5" t="str">
+        <v>screenshots/desktop/03_hero_banner_slider.png</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -596,9 +612,9 @@
         <v>Homepage scrolled to Category Carousel section</v>
       </c>
       <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect all 7 category cards (Living, Dining, Outdoor, Bedroom, Entrance, etc.)
-2. Verify thumbnail imagery and text labels
-3. Verify all card href links point to US catalog paths</v>
+        <v xml:space="preserve">Step 1: Inspect all 7 category cards (Living, Dining, Outdoor, Bedroom, Entrance, etc.)
+Step 2: Verify thumbnail imagery and text labels
+Step 3: Verify all card href links point to US catalog paths</v>
       </c>
       <c r="G6" t="str">
         <v>All category cards display clean imagery and route to US store URLs (e.g. /indoor/shop-by-room/living-room).</v>
@@ -611,6 +627,9 @@
       </c>
       <c r="J6" t="str">
         <v>None. Verified matching AU design baseline.</v>
+      </c>
+      <c r="K6" t="str">
+        <v>comparison/COMPARISON_PASS_02_CATEGORY_CAROUSEL.png</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -630,9 +649,9 @@
         <v>Homepage scrolled past category carousel</v>
       </c>
       <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Locate About Us brand block
-2. Verify copy layout, headline, paragraph typography, and image column
-3. Verify CTA button pill styling and destination</v>
+        <v xml:space="preserve">Step 1: Locate About Us brand block
+Step 2: Verify copy layout, headline, paragraph typography, and image column
+Step 3: Verify CTA button pill styling and destination</v>
       </c>
       <c r="G7" t="str">
         <v>Clean 2-column layout with brand narrative ("Distinctive Living Designed for Designers") and lifestyle imagery.</v>
@@ -645,6 +664,9 @@
       </c>
       <c r="J7" t="str">
         <v>None. Verified matching approved design baseline.</v>
+      </c>
+      <c r="K7" t="str">
+        <v>screenshots/desktop/05_about_us_brand_story.png</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -664,9 +686,9 @@
         <v>Homepage scrolled to Video Showcase section</v>
       </c>
       <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Locate video container
-2. Verify 16:9 aspect ratio and responsive iframe embed
-3. Verify play controls and headline text</v>
+        <v xml:space="preserve">Step 1: Locate video container
+Step 2: Verify 16:9 aspect ratio and responsive iframe embed
+Step 3: Verify play controls and headline text</v>
       </c>
       <c r="G8" t="str">
         <v>Responsive video player block renders without layout breakage or horizontal overflow.</v>
@@ -679,6 +701,9 @@
       </c>
       <c r="J8" t="str">
         <v>None. Verified matching approved design baseline.</v>
+      </c>
+      <c r="K8" t="str">
+        <v>screenshots/desktop/06_b2b_video_block.png</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -698,9 +723,9 @@
         <v>Homepage scrolled to Fresh Ideas / Content Hub section</v>
       </c>
       <c r="F9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect cards in `home-page-fresh-ideas` block
-2. Read article titles, dates, and preview summaries
-3. Cross-verify manually in live browsing mode</v>
+        <v xml:space="preserve">Step 1: Inspect cards in `home-page-fresh-ideas` block
+Step 2: Read article titles, dates, and preview summaries
+Step 3: Cross-verify manually in live browsing mode</v>
       </c>
       <c r="G9" t="str">
         <v>Editorial journal articles with professional photography and internal links.</v>
@@ -713,6 +738,9 @@
       </c>
       <c r="J9" t="str">
         <v>None. Manually verified passing by QA Lead.</v>
+      </c>
+      <c r="K9" t="str">
+        <v>screenshots/desktop/07_recent_articles_journal.png</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -732,9 +760,9 @@
         <v>Homepage scrolled to Instagram section above footer</v>
       </c>
       <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Locate Instagram block container
-2. Verify "@Globewest" header and feed photos
-3. Cross-verify manually in live browsing session</v>
+        <v xml:space="preserve">Step 1: Locate Instagram block container
+Step 2: Verify "@Globewest" header and feed photos
+Step 3: Cross-verify manually in live browsing session</v>
       </c>
       <c r="G10" t="str">
         <v>Live photo grid displaying tagged community styling images.</v>
@@ -747,6 +775,9 @@
       </c>
       <c r="J10" t="str">
         <v>None. Manually verified passing by QA Lead.</v>
+      </c>
+      <c r="K10" t="str">
+        <v>screenshots/desktop/08_instagram_feed.png</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -766,9 +797,9 @@
         <v>Homepage scrolled above footer container</v>
       </c>
       <c r="F11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect DOM for block container `home-us-seo-text`
-2. Verify presence of expandable SEO narrative copy
-3. Check computed visibility style</v>
+        <v xml:space="preserve">Step 1: Inspect DOM for block container `home-us-seo-text`
+Step 2: Verify presence of expandable SEO narrative copy
+Step 3: Check computed visibility style</v>
       </c>
       <c r="G11" t="str">
         <v>SEO block renders "Distinctive Living" narrative text block.</v>
@@ -781,6 +812,9 @@
       </c>
       <c r="J11" t="str">
         <v>None. Verified matching approved design specification.</v>
+      </c>
+      <c r="K11" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -800,9 +834,9 @@
         <v>Full homepage DOM loaded</v>
       </c>
       <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect links in the page footer under "CUSTOMER SUPPORT"
-2. Hover over "Shop Outlet" and observe the target URL preview
-3. Click "Shop Outlet" and verify navigation</v>
+        <v xml:space="preserve">Step 1: Inspect links in the page footer under "CUSTOMER SUPPORT"
+Step 2: Hover over "Shop Outlet" and observe the target URL preview
+Step 3: Click "Shop Outlet" and verify navigation</v>
       </c>
       <c r="G12" t="str">
         <v>All links must resolve within the US domestic domain (mcstaging2.globewest.com) or point to an internal US clearance section.</v>
@@ -815,6 +849,9 @@
       </c>
       <c r="J12" t="str">
         <v>Storefront footer "Shop Outlet" link leaks US buyers to external Australian website (https://globewestoutlet.com.au/).</v>
+      </c>
+      <c r="K12" t="str">
+        <v>screenshots/defects/DEFECT_AU_OUTLET_URL_FOOTER_RED_BOX.png</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -834,9 +871,9 @@
         <v>Viewport set to 390x844 (iPhone 14/15)</v>
       </c>
       <c r="F13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load US Homepage in mobile viewport
-2. Measure document.documentElement.scrollWidth vs clientWidth
-3. Inspect mobile hamburger menu, hero slider, and category touch stacking</v>
+        <v xml:space="preserve">Step 1: Load US Homepage in mobile viewport
+Step 2: Measure document.documentElement.scrollWidth vs clientWidth
+Step 3: Inspect mobile hamburger menu, hero slider, and category touch stacking</v>
       </c>
       <c r="G13" t="str">
         <v>Zero horizontal scrolling (scrollWidth &lt;= clientWidth). All sections stack neatly for touch navigation.</v>
@@ -849,6 +886,9 @@
       </c>
       <c r="J13" t="str">
         <v>None. Verified passing mobile responsive standard.</v>
+      </c>
+      <c r="K13" t="str">
+        <v>comparison/COMPARISON_PASS_04_MOBILE_RESPONSIVE.png</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -868,9 +908,9 @@
         <v>User session is unauthenticated guest</v>
       </c>
       <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Browse homepage sections
-2. Verify absence of wholesale prices and trade margin badges
-3. Verify Trade Pricing toggle is hidden</v>
+        <v xml:space="preserve">Step 1: Browse homepage sections
+Step 2: Verify absence of wholesale prices and trade margin badges
+Step 3: Verify Trade Pricing toggle is hidden</v>
       </c>
       <c r="G14" t="str">
         <v>Strict price masking: Trade pricing toggle hidden, wholesale figures masked.</v>
@@ -883,6 +923,9 @@
       </c>
       <c r="J14" t="str">
         <v>None. Verified matching approved security and auth matrix.</v>
+      </c>
+      <c r="K14" t="str">
+        <v>comparison/COMPARISON_PASS_03_DUAL_AUTH_MATRIX.png</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -902,9 +945,9 @@
         <v>Logged in with verified trade customer credentials</v>
       </c>
       <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log in via /customer/account/login/
-2. Navigate to US Homepage
-3. Verify presence of Trade Pricing Toggle ("Trade" vs "MSRP") in header</v>
+        <v xml:space="preserve">Step 1: Log in via /customer/account/login/
+Step 2: Navigate to US Homepage
+Step 3: Verify presence of Trade Pricing Toggle ("Trade" vs "MSRP") in header</v>
       </c>
       <c r="G15" t="str">
         <v>Header renders Trade Pricing Toggle button. User recognized as Trade Customer.</v>
@@ -917,6 +960,9 @@
       </c>
       <c r="J15" t="str">
         <v>None. Verified matching approved trade portal specification.</v>
+      </c>
+      <c r="K15" t="str">
+        <v>screenshots/desktop/10_authenticated_trade_homepage.png</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -936,11 +982,8 @@
         <v>Full homepage DOM loaded with AxeBuilder rulesets</v>
       </c>
       <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Run AxeBuilder against WCAG
-2.0,
-2.1,
-2.2 Level A and AA rules
-2. Inspect for critical violations (contrast, alt text, ARIA roles, landmarks)</v>
+        <v xml:space="preserve">Step 1: Run AxeBuilder against WCAG 2.0, 2.1, 2.2 Level A and AA rules
+Step 2: Inspect for critical violations (contrast, alt text, ARIA roles, landmarks)</v>
       </c>
       <c r="G16" t="str">
         <v>Zero critical or blocking WCAG 2.2 AA accessibility violations on the homepage.</v>
@@ -954,10 +997,240 @@
       <c r="J16" t="str">
         <v>None. Passed Phase 1 accessibility gate.</v>
       </c>
+      <c r="K16" t="str">
+        <v>scripts/ticket_homepage_audit.spec.js</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-HP-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Social Proof / Instagram Feed</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Verify Instagram Social Gallery Grid &amp; Lightbox Modal Preview</v>
+      </c>
+      <c r="E17" t="str">
+        <v>US Homepage loaded in desktop viewport</v>
+      </c>
+      <c r="F17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Scroll to homepage social proof gallery
+Step 2: Inspect user-generated lifestyle image tiles
+Step 3: Click on a gallery image
+Step 4: Verify lightbox modal popup with tagged product link.</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Gallery renders authentic high-res lifestyle imagery; clicking opens lightbox modal with product details and link to US PDP without AU leakage.</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Social proof gallery loads lifestyle imagery; modal view displays clean product links.</v>
+      </c>
+      <c r="I17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J17" t="str">
+        <v>None. Verified matching approved social gallery spec.</v>
+      </c>
+      <c r="K17" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-HP-17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Newsletter Subscription</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Verify Homepage Footer Newsletter Email Input Validation</v>
+      </c>
+      <c r="E18" t="str">
+        <v>US Homepage loaded</v>
+      </c>
+      <c r="F18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Scroll to newsletter signup section
+Step 2: Submit empty email input
+Step 3: Enter invalid email string ("test@invalid")
+Step 4: Enter valid email and click subscribe.</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Inline error prompt highlights invalid email; valid email triggers success acknowledgment toast.</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Form performs client-side email format validation; error states and success notifications render properly.</v>
+      </c>
+      <c r="I18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J18" t="str">
+        <v>None. Verified standard Magento newsletter integration.</v>
+      </c>
+      <c r="K18" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-HP-18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Performance &amp; Lazy Loading</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Verify Image Lazy Loading &amp; Zero Placeholder Delivery on Initial Load</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Network throttled to Fast 3G in Chrome DevTools</v>
+      </c>
+      <c r="F19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Hard refresh US homepage
+Step 2: Inspect above-the-fold vs below-the-fold images
+Step 3: Assert loading="lazy" attribute on below-the-fold media
+Step 4: Check that no image src contains /placeholder/default/.</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Below-the-fold imagery utilizes lazy loading; initial payload is optimized; zero default placeholder icons rendered.</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Lazy loading active across secondary carousels; zero placeholder leaks detected.</v>
+      </c>
+      <c r="I19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J19" t="str">
+        <v>None. Verified asset integrity and performance standard.</v>
+      </c>
+      <c r="K19" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-HP-19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mobile Sticky Header</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Verify Mobile Viewport Sticky Header Traversal on Touch Scroll</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Mobile Viewport 390x844 (iPhone 14/15 profile)</v>
+      </c>
+      <c r="F20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Load US homepage on mobile viewport
+Step 2: Scroll down 600px
+Step 3: Verify sticky header elevation, logo sizing, and hamburger icon visibility
+Step 4: Scroll up to verify header transition.</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Header sticks to top with compact height; hamburger menu and cart badge remain easily clickable without covering content.</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Mobile sticky header transitions smoothly with proper z-index elevation and touch access.</v>
+      </c>
+      <c r="I20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J20" t="str">
+        <v>None. Verified mobile responsiveness.</v>
+      </c>
+      <c r="K20" t="str">
+        <v>screenshots/mobile/01_mobile_homepage_top.png</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-HP-20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Featured Collections Grid</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Verify Featured Collections Category Tiles Grid &amp; Responsive Wrapping</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Viewport resized across Desktop (1440px), Tablet (768px), and Mobile (390px)</v>
+      </c>
+      <c r="F21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Inspect Featured Collections section
+Step 2: Verify 4-column layout on desktop
+Step 3: Verify 2-column layout on tablet
+Step 4: Verify 1-column stack or swipe carousel on mobile.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Tiles wrap cleanly according to responsive breakpoints without overflow or truncated headings.</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Responsive breakpoints adapt cleanly across 1440px, 768px, and 390px widths.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J21" t="str">
+        <v>None. Verified responsive grid parity.</v>
+      </c>
+      <c r="K21" t="str">
+        <v>screenshots/desktop/01_desktop_homepage_full.png</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-HP-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Hero Banner Carousel Controls</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Guest (Logged Out)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Verify Hero Carousel Keyboard Arrows, Dot Navigation &amp; Pause on Hover</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Hero banner slider rendered on US homepage</v>
+      </c>
+      <c r="F22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Focus on hero carousel pagination dots using Tab key
+Step 2: Press left/right arrow keys to switch slides
+Step 3: Hover mouse cursor over active slide to verify auto-rotation pauses.</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Carousel supports accessible keyboard navigation; pagination dots update aria-selected; rotation pauses during user hover/focus.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Slider controls support accessible navigation and pause on hover; slide indicator updates accurately.</v>
+      </c>
+      <c r="I22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J22" t="str">
+        <v>None. Verified WCAG keyboard interaction standard.</v>
+      </c>
+      <c r="K22" t="str">
+        <v>comparison/COMPARISON_PASS_01_HERO_BANNER_SLIDER.png</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>